--- a/astro-site/public/dl/chocolate-shop-checklist-templates/04-chocolate-shop-duties-by-role.xlsx
+++ b/astro-site/public/dl/chocolate-shop-checklist-templates/04-chocolate-shop-duties-by-role.xlsx
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Clean the tempering machine after every use</t>
+          <t>Clean the tempering machine after every use, and always before switching from milk to dark or white: milk carried over into dark chocolate is an undeclared allergen</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Set up the sample area: tongs, toothpicks or single-use cups, never bare hands (FDA 3-301.11)</t>
+          <t>Set up the sample area: one set of tongs per tray (nut and peanut items never share tongs), toothpicks or single-use cups, never bare hands (FDA 3-301.11)</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Build custom bonbon gift boxes with gloves or tongs, never bare hands (FDA 3-301.11)</t>
+          <t>Build custom bonbon gift boxes with gloves or tongs, never bare hands (FDA 3-301.11); for an allergy request, fresh gloves and pieces from untouched trays</t>
         </is>
       </c>
       <c r="C15" s="18" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Move products from the display case to the cool room</t>
+          <t>Move products from the display case to the cool room; any TCS fresh-cream item to the fridge (41 °F or below)</t>
         </is>
       </c>
       <c r="C29" s="16" t="inlineStr">
